--- a/sinai_n825/cluster_assignments_sinai_n825_15topics_16clusters_v1.xlsx
+++ b/sinai_n825/cluster_assignments_sinai_n825_15topics_16clusters_v1.xlsx
@@ -5,25 +5,26 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jcvioffice365-my.sharepoint.com/personal/bpeng_jcvi_org/Documents/Documents/GitHub/endotyping_covid/sinai_n825/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bpeng\Documents\pasc_endotyping\github_files\sinai_n825\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:9_{9EEA7917-FAC0-4F8C-90B3-B317322A08CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E035EB23-CD44-4712-B295-F315E664D76E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DDC1E4-5306-4A36-AC64-6458330421B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCDD06BF-F8C4-4633-8CCC-4A11819212F0}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="4" xr2:uid="{DCDD06BF-F8C4-4633-8CCC-4A11819212F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Cluster_assignments" sheetId="1" r:id="rId1"/>
     <sheet name="Top6_signature_symptoms" sheetId="2" r:id="rId2"/>
-    <sheet name="Top3_organ_systems" sheetId="3" r:id="rId3"/>
-    <sheet name="Severity_scores" sheetId="4" r:id="rId4"/>
+    <sheet name="Top3_organ_systems" sheetId="5" r:id="rId3"/>
+    <sheet name="Top3_organ_systems_row" sheetId="3" r:id="rId4"/>
+    <sheet name="Severity_scores" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4375" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4426" uniqueCount="151">
   <si>
     <t>Subject_ID</t>
   </si>
@@ -413,6 +414,157 @@
   </si>
   <si>
     <t>LC 131</t>
+  </si>
+  <si>
+    <t>['neurological', 'sensory changes', 'pulmonary']</t>
+  </si>
+  <si>
+    <t>['g.i', 'temperature regulation', 'sexual/hormonal function']</t>
+  </si>
+  <si>
+    <t>['sexual/hormonal function', 'sensory changes', 'musculo-skeletal']</t>
+  </si>
+  <si>
+    <t>['sensory changes', 'neurological', 'musculo-skeletal']</t>
+  </si>
+  <si>
+    <t>['neurological', 'sensory changes', 'g.i']</t>
+  </si>
+  <si>
+    <t>['sensory changes', 'neurological', 'sexual/hormonal function']</t>
+  </si>
+  <si>
+    <t>['sensory changes', 'sexual/hormonal function', 'neurological']</t>
+  </si>
+  <si>
+    <t>['neurological', 'sensory changes', 'cognitive/psych']</t>
+  </si>
+  <si>
+    <t>['sexual/hormonal function', 'musculo-skeletal', 'g.i']</t>
+  </si>
+  <si>
+    <t>['g.i', 'cognitive/psych', 'neurological']</t>
+  </si>
+  <si>
+    <t>E5</t>
+  </si>
+  <si>
+    <t>E6</t>
+  </si>
+  <si>
+    <t>E7</t>
+  </si>
+  <si>
+    <t>E8</t>
+  </si>
+  <si>
+    <t>E9</t>
+  </si>
+  <si>
+    <t>E10</t>
+  </si>
+  <si>
+    <t>E11</t>
+  </si>
+  <si>
+    <t>E12</t>
+  </si>
+  <si>
+    <r>
+      <t>['</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pulmonary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>', 'cognitive/psych', '</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cardiovascular</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>']</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>['</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cardiovascular</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>', '</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pulmonary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>', 'neurological']</t>
+    </r>
+  </si>
+  <si>
+    <t>E13</t>
   </si>
 </sst>
 </file>
@@ -962,7 +1114,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1005,10 +1157,11 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1126,6 +1279,72 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1208833</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>55880</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>296555</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>172811</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EDAA2A1-197F-CD2D-CE07-9566D2DCF546}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5617547" y="55880"/>
+          <a:ext cx="3205788" cy="3269978"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>12853</xdr:colOff>
       <xdr:row>0</xdr:row>
@@ -1177,7 +1396,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1567,7 +1786,7 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="20" t="s">
         <v>124</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -23813,6 +24032,248 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F9D99FF-2E47-4186-9ED4-7A56B95E285B}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+    </row>
+    <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+    </row>
+    <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+    </row>
+    <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{677EEC8D-EBBD-4146-A189-27D86B7B0F15}">
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -23830,11 +24291,11 @@
       <c r="B1" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
     </row>
     <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
@@ -24117,7 +24578,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C5EB264-CFCE-4E9C-921D-821B5885EC2F}">
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
